--- a/templates/ERC000029/metadata_template_ERC000029.xlsx
+++ b/templates/ERC000029/metadata_template_ERC000029.xlsx
@@ -25,7 +25,7 @@
     <definedName name="hostdiseaseoutcome">'cv_sample'!$X$1:$X$3</definedName>
     <definedName name="hosthealthstate">'cv_sample'!$AC$1:$AC$14</definedName>
     <definedName name="hostsex">'cv_sample'!$AD$1:$AD$17</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$85</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
     <definedName name="Isthesequencedpathogenhostassociated">'cv_sample'!$AH$1:$AH$2</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="680">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="682">
   <si>
     <t>alias</t>
   </si>
@@ -563,6 +563,9 @@
     <t>DNBSEQ-G50</t>
   </si>
   <si>
+    <t>DNBSEQ-G800</t>
+  </si>
+  <si>
     <t>DNBSEQ-T10x4RS</t>
   </si>
   <si>
@@ -726,6 +729,9 @@
   </si>
   <si>
     <t>UG 100</t>
+  </si>
+  <si>
+    <t>Vega</t>
   </si>
   <si>
     <t>instrument_model</t>
@@ -2608,7 +2614,7 @@
         <v>143</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2652,7 +2658,7 @@
         <v>144</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -2679,7 +2685,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N85"/>
+  <dimension ref="G1:N87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3398,6 +3404,16 @@
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="86" spans="14:14">
+      <c r="N86" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="87" spans="14:14">
+      <c r="N87" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3419,27 +3435,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3459,122 +3475,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -3598,300 +3614,300 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="2" spans="1:50" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
     </row>
   </sheetData>
@@ -3935,253 +3951,253 @@
   <sheetData>
     <row r="1" spans="7:34">
       <c r="G1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="H1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="S1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="V1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="X1" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="AC1" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="AD1" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="AH1" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="2" spans="7:34">
       <c r="G2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="I2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="S2" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="V2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="X2" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="AC2" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="AD2" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="AH2" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="3" spans="7:34">
       <c r="G3" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I3" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="V3" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="X3" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="AC3" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AD3" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="4" spans="7:34">
       <c r="I4" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="V4" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AC4" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AD4" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="5" spans="7:34">
       <c r="I5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="V5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AC5" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="AD5" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="6" spans="7:34">
       <c r="I6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="V6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AC6" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="AD6" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="7" spans="7:34">
       <c r="I7" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="V7" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AC7" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="AD7" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="8" spans="7:34">
       <c r="I8" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="V8" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AC8" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="AD8" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="9" spans="7:34">
       <c r="I9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="V9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AC9" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AD9" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="10" spans="7:34">
       <c r="I10" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="V10" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AC10" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AD10" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="11" spans="7:34">
       <c r="I11" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="V11" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AC11" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AD11" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="12" spans="7:34">
       <c r="I12" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="V12" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AC12" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="AD12" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
     </row>
     <row r="13" spans="7:34">
       <c r="I13" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="V13" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AC13" t="s">
+        <v>613</v>
+      </c>
+      <c r="AD13" t="s">
         <v>611</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="14" spans="7:34">
       <c r="I14" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="V14" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AC14" t="s">
+        <v>614</v>
+      </c>
+      <c r="AD14" t="s">
         <v>612</v>
-      </c>
-      <c r="AD14" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="15" spans="7:34">
       <c r="I15" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="V15" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AD15" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="16" spans="7:34">
       <c r="I16" t="s">
+        <v>298</v>
+      </c>
+      <c r="V16" t="s">
         <v>296</v>
-      </c>
-      <c r="V16" t="s">
-        <v>294</v>
       </c>
       <c r="AD16" t="s">
         <v>116</v>
@@ -4189,2141 +4205,2141 @@
     </row>
     <row r="17" spans="9:30">
       <c r="I17" t="s">
+        <v>299</v>
+      </c>
+      <c r="V17" t="s">
         <v>297</v>
       </c>
-      <c r="V17" t="s">
-        <v>295</v>
-      </c>
       <c r="AD17" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="18" spans="9:30">
       <c r="I18" t="s">
+        <v>300</v>
+      </c>
+      <c r="V18" t="s">
         <v>298</v>
-      </c>
-      <c r="V18" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="19" spans="9:30">
       <c r="I19" t="s">
+        <v>301</v>
+      </c>
+      <c r="V19" t="s">
         <v>299</v>
-      </c>
-      <c r="V19" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="20" spans="9:30">
       <c r="I20" t="s">
+        <v>302</v>
+      </c>
+      <c r="V20" t="s">
         <v>300</v>
-      </c>
-      <c r="V20" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="21" spans="9:30">
       <c r="I21" t="s">
+        <v>303</v>
+      </c>
+      <c r="V21" t="s">
         <v>301</v>
-      </c>
-      <c r="V21" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="22" spans="9:30">
       <c r="I22" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="V22" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="23" spans="9:30">
       <c r="I23" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="V23" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="24" spans="9:30">
       <c r="I24" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="V24" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="25" spans="9:30">
       <c r="I25" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="V25" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="26" spans="9:30">
       <c r="I26" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="V26" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="27" spans="9:30">
       <c r="I27" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="V27" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="28" spans="9:30">
       <c r="I28" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="V28" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="29" spans="9:30">
       <c r="I29" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="V29" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="30" spans="9:30">
       <c r="I30" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="V30" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="31" spans="9:30">
       <c r="I31" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="V31" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="32" spans="9:30">
       <c r="I32" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="V32" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="33" spans="9:22">
       <c r="I33" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="V33" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
     </row>
     <row r="34" spans="9:22">
       <c r="I34" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="V34" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="35" spans="9:22">
       <c r="I35" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="V35" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="36" spans="9:22">
       <c r="I36" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="V36" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="37" spans="9:22">
       <c r="I37" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="V37" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="38" spans="9:22">
       <c r="I38" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="V38" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="39" spans="9:22">
       <c r="I39" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="V39" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="40" spans="9:22">
       <c r="I40" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="V40" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="41" spans="9:22">
       <c r="I41" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="V41" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="42" spans="9:22">
       <c r="I42" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="V42" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="43" spans="9:22">
       <c r="I43" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="V43" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="44" spans="9:22">
       <c r="I44" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="V44" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="45" spans="9:22">
       <c r="I45" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="V45" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="46" spans="9:22">
       <c r="I46" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="V46" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="47" spans="9:22">
       <c r="I47" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="V47" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="48" spans="9:22">
       <c r="I48" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="V48" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="49" spans="9:22">
       <c r="I49" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="V49" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="50" spans="9:22">
       <c r="I50" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="V50" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="51" spans="9:22">
       <c r="I51" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="V51" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="52" spans="9:22">
       <c r="I52" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="V52" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="53" spans="9:22">
       <c r="I53" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="V53" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="54" spans="9:22">
       <c r="I54" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="V54" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="55" spans="9:22">
       <c r="I55" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="V55" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="56" spans="9:22">
       <c r="I56" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="V56" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="57" spans="9:22">
       <c r="I57" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="V57" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="58" spans="9:22">
       <c r="I58" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="V58" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="59" spans="9:22">
       <c r="I59" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="V59" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="60" spans="9:22">
       <c r="I60" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="V60" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="61" spans="9:22">
       <c r="I61" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="V61" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="62" spans="9:22">
       <c r="I62" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="V62" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="63" spans="9:22">
       <c r="I63" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="V63" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="64" spans="9:22">
       <c r="I64" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="V64" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="65" spans="9:22">
       <c r="I65" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="V65" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="66" spans="9:22">
       <c r="I66" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="V66" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="67" spans="9:22">
       <c r="I67" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="V67" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="68" spans="9:22">
       <c r="I68" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="V68" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="69" spans="9:22">
       <c r="I69" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="V69" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="70" spans="9:22">
       <c r="I70" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="V70" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="71" spans="9:22">
       <c r="I71" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="V71" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="72" spans="9:22">
       <c r="I72" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="V72" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="73" spans="9:22">
       <c r="I73" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="V73" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="74" spans="9:22">
       <c r="I74" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="V74" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="75" spans="9:22">
       <c r="I75" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="V75" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="76" spans="9:22">
       <c r="I76" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="V76" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="77" spans="9:22">
       <c r="I77" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="V77" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="78" spans="9:22">
       <c r="I78" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="V78" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="79" spans="9:22">
       <c r="I79" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="V79" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="80" spans="9:22">
       <c r="I80" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="V80" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="81" spans="9:22">
       <c r="I81" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="V81" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="82" spans="9:22">
       <c r="I82" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="V82" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="83" spans="9:22">
       <c r="I83" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="V83" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="84" spans="9:22">
       <c r="I84" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="V84" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="85" spans="9:22">
       <c r="I85" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="V85" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="86" spans="9:22">
       <c r="I86" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="V86" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="87" spans="9:22">
       <c r="I87" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="V87" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="88" spans="9:22">
       <c r="I88" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="V88" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="89" spans="9:22">
       <c r="I89" t="s">
+        <v>371</v>
+      </c>
+      <c r="V89" t="s">
         <v>369</v>
-      </c>
-      <c r="V89" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="90" spans="9:22">
       <c r="I90" t="s">
+        <v>372</v>
+      </c>
+      <c r="V90" t="s">
         <v>370</v>
-      </c>
-      <c r="V90" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="91" spans="9:22">
       <c r="I91" t="s">
+        <v>373</v>
+      </c>
+      <c r="V91" t="s">
         <v>371</v>
-      </c>
-      <c r="V91" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="92" spans="9:22">
       <c r="I92" t="s">
+        <v>374</v>
+      </c>
+      <c r="V92" t="s">
         <v>372</v>
-      </c>
-      <c r="V92" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="93" spans="9:22">
       <c r="I93" t="s">
+        <v>375</v>
+      </c>
+      <c r="V93" t="s">
         <v>373</v>
-      </c>
-      <c r="V93" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="94" spans="9:22">
       <c r="I94" t="s">
+        <v>376</v>
+      </c>
+      <c r="V94" t="s">
         <v>374</v>
-      </c>
-      <c r="V94" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="95" spans="9:22">
       <c r="I95" t="s">
+        <v>377</v>
+      </c>
+      <c r="V95" t="s">
         <v>375</v>
-      </c>
-      <c r="V95" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="96" spans="9:22">
       <c r="I96" t="s">
+        <v>378</v>
+      </c>
+      <c r="V96" t="s">
         <v>376</v>
-      </c>
-      <c r="V96" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="97" spans="9:22">
       <c r="I97" t="s">
+        <v>379</v>
+      </c>
+      <c r="V97" t="s">
         <v>377</v>
-      </c>
-      <c r="V97" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="98" spans="9:22">
       <c r="I98" t="s">
+        <v>380</v>
+      </c>
+      <c r="V98" t="s">
         <v>378</v>
-      </c>
-      <c r="V98" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="99" spans="9:22">
       <c r="I99" t="s">
+        <v>381</v>
+      </c>
+      <c r="V99" t="s">
         <v>379</v>
-      </c>
-      <c r="V99" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="100" spans="9:22">
       <c r="I100" t="s">
+        <v>382</v>
+      </c>
+      <c r="V100" t="s">
         <v>380</v>
-      </c>
-      <c r="V100" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="101" spans="9:22">
       <c r="I101" t="s">
+        <v>383</v>
+      </c>
+      <c r="V101" t="s">
         <v>381</v>
-      </c>
-      <c r="V101" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="102" spans="9:22">
       <c r="I102" t="s">
+        <v>384</v>
+      </c>
+      <c r="V102" t="s">
         <v>382</v>
-      </c>
-      <c r="V102" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="103" spans="9:22">
       <c r="I103" t="s">
+        <v>385</v>
+      </c>
+      <c r="V103" t="s">
         <v>383</v>
-      </c>
-      <c r="V103" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="104" spans="9:22">
       <c r="I104" t="s">
+        <v>386</v>
+      </c>
+      <c r="V104" t="s">
         <v>384</v>
-      </c>
-      <c r="V104" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="105" spans="9:22">
       <c r="I105" t="s">
+        <v>387</v>
+      </c>
+      <c r="V105" t="s">
         <v>385</v>
-      </c>
-      <c r="V105" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="106" spans="9:22">
       <c r="I106" t="s">
+        <v>388</v>
+      </c>
+      <c r="V106" t="s">
         <v>386</v>
-      </c>
-      <c r="V106" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="107" spans="9:22">
       <c r="I107" t="s">
+        <v>389</v>
+      </c>
+      <c r="V107" t="s">
         <v>387</v>
-      </c>
-      <c r="V107" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="108" spans="9:22">
       <c r="I108" t="s">
+        <v>390</v>
+      </c>
+      <c r="V108" t="s">
         <v>388</v>
-      </c>
-      <c r="V108" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="109" spans="9:22">
       <c r="I109" t="s">
+        <v>391</v>
+      </c>
+      <c r="V109" t="s">
         <v>389</v>
-      </c>
-      <c r="V109" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="110" spans="9:22">
       <c r="I110" t="s">
+        <v>392</v>
+      </c>
+      <c r="V110" t="s">
         <v>390</v>
-      </c>
-      <c r="V110" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="111" spans="9:22">
       <c r="I111" t="s">
+        <v>393</v>
+      </c>
+      <c r="V111" t="s">
         <v>391</v>
-      </c>
-      <c r="V111" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="112" spans="9:22">
       <c r="I112" t="s">
+        <v>394</v>
+      </c>
+      <c r="V112" t="s">
         <v>392</v>
-      </c>
-      <c r="V112" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="113" spans="9:22">
       <c r="I113" t="s">
+        <v>395</v>
+      </c>
+      <c r="V113" t="s">
         <v>393</v>
-      </c>
-      <c r="V113" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="114" spans="9:22">
       <c r="I114" t="s">
+        <v>396</v>
+      </c>
+      <c r="V114" t="s">
         <v>394</v>
-      </c>
-      <c r="V114" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="115" spans="9:22">
       <c r="I115" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="V115" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="116" spans="9:22">
       <c r="I116" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="V116" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="117" spans="9:22">
       <c r="I117" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="V117" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="118" spans="9:22">
       <c r="I118" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="V118" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="119" spans="9:22">
       <c r="I119" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="V119" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="120" spans="9:22">
       <c r="I120" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="V120" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="121" spans="9:22">
       <c r="I121" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="V121" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="122" spans="9:22">
       <c r="I122" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="V122" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="123" spans="9:22">
       <c r="I123" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="V123" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="124" spans="9:22">
       <c r="I124" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="V124" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="125" spans="9:22">
       <c r="I125" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="V125" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="126" spans="9:22">
       <c r="I126" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="V126" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="127" spans="9:22">
       <c r="I127" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="V127" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="128" spans="9:22">
       <c r="I128" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="V128" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="129" spans="9:22">
       <c r="I129" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="V129" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="130" spans="9:22">
       <c r="I130" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="V130" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="131" spans="9:22">
       <c r="I131" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="V131" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="132" spans="9:22">
       <c r="I132" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="V132" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="133" spans="9:22">
       <c r="I133" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="V133" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="134" spans="9:22">
       <c r="I134" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="V134" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="135" spans="9:22">
       <c r="I135" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="V135" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="136" spans="9:22">
       <c r="I136" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="V136" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="137" spans="9:22">
       <c r="I137" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="V137" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="138" spans="9:22">
       <c r="I138" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="V138" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="139" spans="9:22">
       <c r="I139" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="V139" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="140" spans="9:22">
       <c r="I140" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="V140" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="141" spans="9:22">
       <c r="I141" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="V141" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="142" spans="9:22">
       <c r="I142" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="V142" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="143" spans="9:22">
       <c r="I143" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="V143" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="144" spans="9:22">
       <c r="I144" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="V144" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="145" spans="9:22">
       <c r="I145" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="V145" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="146" spans="9:22">
       <c r="I146" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="V146" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="147" spans="9:22">
       <c r="I147" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="V147" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="148" spans="9:22">
       <c r="I148" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="V148" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="149" spans="9:22">
       <c r="I149" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="V149" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="150" spans="9:22">
       <c r="I150" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="V150" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="151" spans="9:22">
       <c r="I151" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="V151" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="152" spans="9:22">
       <c r="I152" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="V152" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="153" spans="9:22">
       <c r="I153" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="V153" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="154" spans="9:22">
       <c r="I154" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="V154" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="155" spans="9:22">
       <c r="I155" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="V155" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="156" spans="9:22">
       <c r="I156" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="V156" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="157" spans="9:22">
       <c r="I157" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="V157" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="158" spans="9:22">
       <c r="I158" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="V158" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="159" spans="9:22">
       <c r="I159" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="V159" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="160" spans="9:22">
       <c r="I160" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="V160" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="161" spans="9:22">
       <c r="I161" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="V161" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="162" spans="9:22">
       <c r="I162" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="V162" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="163" spans="9:22">
       <c r="I163" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="V163" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="164" spans="9:22">
       <c r="I164" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="V164" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="165" spans="9:22">
       <c r="I165" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="V165" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="166" spans="9:22">
       <c r="I166" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="V166" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="167" spans="9:22">
       <c r="I167" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="V167" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="168" spans="9:22">
       <c r="I168" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="V168" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="169" spans="9:22">
       <c r="I169" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="V169" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="170" spans="9:22">
       <c r="I170" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="V170" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="171" spans="9:22">
       <c r="I171" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="V171" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="172" spans="9:22">
       <c r="I172" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="V172" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="173" spans="9:22">
       <c r="I173" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="V173" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="174" spans="9:22">
       <c r="I174" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="V174" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="175" spans="9:22">
       <c r="I175" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="V175" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="176" spans="9:22">
       <c r="I176" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="V176" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="177" spans="9:22">
       <c r="I177" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="V177" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="178" spans="9:22">
       <c r="I178" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="V178" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="179" spans="9:22">
       <c r="I179" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="V179" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="180" spans="9:22">
       <c r="I180" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="V180" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="181" spans="9:22">
       <c r="I181" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="V181" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="182" spans="9:22">
       <c r="I182" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="V182" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="183" spans="9:22">
       <c r="I183" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="V183" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="184" spans="9:22">
       <c r="I184" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="V184" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="185" spans="9:22">
       <c r="I185" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="V185" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="186" spans="9:22">
       <c r="I186" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="V186" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="187" spans="9:22">
       <c r="I187" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="V187" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="188" spans="9:22">
       <c r="I188" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="V188" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="189" spans="9:22">
       <c r="I189" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="V189" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="190" spans="9:22">
       <c r="I190" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="V190" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="191" spans="9:22">
       <c r="I191" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="V191" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="192" spans="9:22">
       <c r="I192" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="V192" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="193" spans="9:22">
       <c r="I193" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="V193" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="194" spans="9:22">
       <c r="I194" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="V194" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="195" spans="9:22">
       <c r="I195" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="V195" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="196" spans="9:22">
       <c r="I196" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="V196" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="197" spans="9:22">
       <c r="I197" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="V197" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="198" spans="9:22">
       <c r="I198" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="V198" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="199" spans="9:22">
       <c r="I199" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="V199" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="200" spans="9:22">
       <c r="I200" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="V200" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="201" spans="9:22">
       <c r="I201" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="V201" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="202" spans="9:22">
       <c r="I202" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="V202" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="203" spans="9:22">
       <c r="I203" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="V203" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="204" spans="9:22">
       <c r="I204" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="V204" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="205" spans="9:22">
       <c r="I205" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="V205" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="206" spans="9:22">
       <c r="I206" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="V206" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="207" spans="9:22">
       <c r="I207" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="V207" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="208" spans="9:22">
       <c r="I208" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="V208" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="209" spans="9:22">
       <c r="I209" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="V209" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="210" spans="9:22">
       <c r="I210" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="V210" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="211" spans="9:22">
       <c r="I211" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="V211" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="212" spans="9:22">
       <c r="I212" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="V212" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="213" spans="9:22">
       <c r="I213" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="V213" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="214" spans="9:22">
       <c r="I214" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="V214" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="215" spans="9:22">
       <c r="I215" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="V215" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="216" spans="9:22">
       <c r="I216" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="V216" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="217" spans="9:22">
       <c r="I217" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="V217" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="218" spans="9:22">
       <c r="I218" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="V218" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="219" spans="9:22">
       <c r="I219" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="V219" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="220" spans="9:22">
       <c r="I220" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="V220" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="221" spans="9:22">
       <c r="I221" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="V221" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="222" spans="9:22">
       <c r="I222" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="V222" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="223" spans="9:22">
       <c r="I223" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="V223" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="224" spans="9:22">
       <c r="I224" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="V224" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="225" spans="9:22">
       <c r="I225" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="V225" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
     </row>
     <row r="226" spans="9:22">
       <c r="I226" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="V226" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="227" spans="9:22">
       <c r="I227" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="V227" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="228" spans="9:22">
       <c r="I228" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="V228" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="229" spans="9:22">
       <c r="I229" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="V229" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="230" spans="9:22">
       <c r="I230" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="V230" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="231" spans="9:22">
       <c r="I231" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="V231" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="232" spans="9:22">
       <c r="I232" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="V232" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="233" spans="9:22">
       <c r="I233" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="V233" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="234" spans="9:22">
       <c r="I234" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="V234" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="235" spans="9:22">
       <c r="I235" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="V235" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="236" spans="9:22">
       <c r="I236" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="V236" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="237" spans="9:22">
       <c r="I237" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="V237" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="238" spans="9:22">
       <c r="I238" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="V238" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="239" spans="9:22">
       <c r="I239" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="V239" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="240" spans="9:22">
       <c r="I240" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="V240" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="241" spans="9:22">
       <c r="I241" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="V241" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="242" spans="9:22">
       <c r="I242" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="V242" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="243" spans="9:22">
       <c r="I243" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="V243" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="244" spans="9:22">
       <c r="I244" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="V244" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="245" spans="9:22">
       <c r="I245" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="V245" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="246" spans="9:22">
       <c r="I246" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="V246" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="247" spans="9:22">
       <c r="I247" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="V247" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="248" spans="9:22">
       <c r="I248" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="V248" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="249" spans="9:22">
       <c r="I249" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="V249" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="250" spans="9:22">
       <c r="I250" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="V250" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="251" spans="9:22">
       <c r="I251" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="V251" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="252" spans="9:22">
       <c r="I252" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="V252" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="253" spans="9:22">
       <c r="I253" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="V253" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="254" spans="9:22">
       <c r="I254" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="V254" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="255" spans="9:22">
       <c r="I255" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="V255" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="256" spans="9:22">
       <c r="I256" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="V256" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="257" spans="9:22">
       <c r="I257" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="V257" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="258" spans="9:22">
       <c r="I258" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="V258" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="259" spans="9:22">
       <c r="I259" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="V259" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="260" spans="9:22">
       <c r="I260" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="V260" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="261" spans="9:22">
       <c r="I261" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="V261" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="262" spans="9:22">
       <c r="I262" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="V262" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="263" spans="9:22">
       <c r="I263" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="V263" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="264" spans="9:22">
       <c r="I264" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="V264" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="265" spans="9:22">
       <c r="I265" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="V265" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="266" spans="9:22">
       <c r="I266" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="V266" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="267" spans="9:22">
       <c r="I267" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="V267" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="268" spans="9:22">
       <c r="I268" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="V268" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="269" spans="9:22">
       <c r="I269" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="V269" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="270" spans="9:22">
       <c r="I270" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="V270" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="271" spans="9:22">
       <c r="I271" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="V271" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="272" spans="9:22">
       <c r="I272" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="V272" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="273" spans="9:22">
       <c r="I273" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="V273" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="274" spans="9:22">
       <c r="V274" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="275" spans="9:22">
       <c r="V275" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="276" spans="9:22">
       <c r="V276" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="277" spans="9:22">
       <c r="V277" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="278" spans="9:22">
       <c r="V278" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="279" spans="9:22">
       <c r="V279" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="280" spans="9:22">
       <c r="V280" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
     </row>
     <row r="281" spans="9:22">
       <c r="V281" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="282" spans="9:22">
       <c r="V282" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
     </row>
     <row r="283" spans="9:22">
       <c r="V283" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="284" spans="9:22">
       <c r="V284" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
     </row>
     <row r="285" spans="9:22">
       <c r="V285" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="286" spans="9:22">
       <c r="V286" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="287" spans="9:22">
       <c r="V287" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="288" spans="9:22">
       <c r="V288" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="289" spans="22:22">
       <c r="V289" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000029/metadata_template_ERC000029.xlsx
+++ b/templates/ERC000029/metadata_template_ERC000029.xlsx
@@ -21,12 +21,12 @@
     <definedName name="countryoftravel">'cv_sample'!$I$1:$I$273</definedName>
     <definedName name="environmentalsample">'cv_sample'!$S$1:$S$2</definedName>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$V$1:$V$289</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$V$1:$V$294</definedName>
     <definedName name="hostdiseaseoutcome">'cv_sample'!$X$1:$X$3</definedName>
     <definedName name="hosthealthstate">'cv_sample'!$AC$1:$AC$14</definedName>
     <definedName name="hostsex">'cv_sample'!$AD$1:$AD$17</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$86</definedName>
-    <definedName name="Isthesequencedpathogenhostassociated">'cv_sample'!$AH$1:$AH$2</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
+    <definedName name="isthesequencedpathogenhostassociated">'cv_sample'!$AH$1:$AH$2</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="974" uniqueCount="681">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="685">
   <si>
     <t>alias</t>
   </si>
@@ -563,6 +563,9 @@
     <t>DNBSEQ-G50</t>
   </si>
   <si>
+    <t>DNBSEQ-G800</t>
+  </si>
+  <si>
     <t>DNBSEQ-T10x4RS</t>
   </si>
   <si>
@@ -848,13 +851,13 @@
     <t>(Optional) Free-form text describing the sample, its origin, and its method of isolation.</t>
   </si>
   <si>
-    <t>sample storage conditions</t>
+    <t>sample_storage_conditions</t>
   </si>
   <si>
     <t>(Optional) Conditions at which sample was stored, usually storage temperature, duration and location. in soil context: explain how and for how long the soil sample was stored before dna extraction (fresh/frozen/other).</t>
   </si>
   <si>
-    <t>subject exposure</t>
+    <t>subject_exposure</t>
   </si>
   <si>
     <t>(Optional) Exposure of the subject to infected human or animals, such as poultry, wild bird or swine. if multiple exposures are applicable, please state them separated by semicolon. example: poultry; wild bird</t>
@@ -869,7 +872,7 @@
     <t>travel-related</t>
   </si>
   <si>
-    <t>travel-relation</t>
+    <t>travelrelation</t>
   </si>
   <si>
     <t>(Optional) Designates the relation of the main diagnosis to the patient's travel.</t>
@@ -881,7 +884,7 @@
     <t>during travel</t>
   </si>
   <si>
-    <t>clinical setting</t>
+    <t>clinical_setting</t>
   </si>
   <si>
     <t>(Optional) The timing of the clinic visit in relation to travel.</t>
@@ -1706,7 +1709,7 @@
     <t>Zimbabwe</t>
   </si>
   <si>
-    <t>country of travel</t>
+    <t>country_of_travel</t>
   </si>
   <si>
     <t>(Optional) The name of the country of patient's travel.</t>
@@ -1718,7 +1721,7 @@
     <t>(Mandatory) Name of persons or institute who collected the specimen</t>
   </si>
   <si>
-    <t>collection date</t>
+    <t>collection_date</t>
   </si>
   <si>
     <t>(Mandatory) The date the sample was collected with the intention of sequencing, either as an instance (single point in time) or interval. in case no exact time is available, the date/time can be right truncated i.e. all of these are valid iso8601 compliant times: 2008-01-23t19:23:10+00:00; 2008-01-23t19:23:10; 2008-01-23; 2008-01; 2008.</t>
@@ -1730,19 +1733,19 @@
     <t>(Optional) The altitude of the sample is the vertical distance between earth's surface above sea level and the sampled position in the air. (Units: m)</t>
   </si>
   <si>
-    <t>geographic location (latitude)</t>
+    <t>geographic_location_latitude</t>
   </si>
   <si>
     <t>(Mandatory) The geographical origin of the sample as defined by latitude. the values should be reported in decimal degrees and in wgs84 system (Units: DD)</t>
   </si>
   <si>
-    <t>geographic location (longitude)</t>
+    <t>geographic_location_longitude</t>
   </si>
   <si>
     <t>(Mandatory) The geographical origin of the sample as defined by longitude. the values should be reported in decimal degrees and in wgs84 system (Units: DD)</t>
   </si>
   <si>
-    <t>geographic location (region and locality)</t>
+    <t>geographic_location_region_and_locality</t>
   </si>
   <si>
     <t>(Optional) The geographical origin of the sample as defined by the specific region name followed by the locality name.</t>
@@ -1754,16 +1757,16 @@
     <t>(Optional) Name of the expert who identified the specimen taxonomically</t>
   </si>
   <si>
-    <t>subject exposure duration</t>
-  </si>
-  <si>
-    <t>(Optional) Duration of the exposure of the subject to an infected human or animal. if multiple exposures are applicable, please state their duration in the same order in which you reported the exposure in the field 'subject exposure'. example: 1 day; 0.33 days (Units: year)</t>
-  </si>
-  <si>
-    <t>amount or size of sample collected</t>
-  </si>
-  <si>
-    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: m3)</t>
+    <t>subject_exposure_duration</t>
+  </si>
+  <si>
+    <t>(Optional) Duration of the exposure of the subject to an infected human or animal. if multiple exposures are applicable, please state their duration in the same order in which you reported the exposure in the field 'subject exposure'. example: 1 day; 0.33 days (Units: day)</t>
+  </si>
+  <si>
+    <t>amount_or_size_of_sample_collected</t>
+  </si>
+  <si>
+    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: kg)</t>
   </si>
   <si>
     <t>No</t>
@@ -1808,7 +1811,7 @@
     <t>Czechia</t>
   </si>
   <si>
-    <t>East Timor</t>
+    <t>Eswatini</t>
   </si>
   <si>
     <t>Falkland Islands (Islas Malvinas)</t>
@@ -1820,12 +1823,21 @@
     <t>Kerguelen Archipelago</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Mediterranean Sea</t>
   </si>
   <si>
+    <t>Micronesia, Federated States of</t>
+  </si>
+  <si>
     <t>Myanmar</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1883,13 +1895,13 @@
     <t>restricted access</t>
   </si>
   <si>
-    <t>geographic location (country and/or sea)</t>
+    <t>geographic_location_country_andor_sea</t>
   </si>
   <si>
     <t>(Mandatory) The geographical origin of where the sample was collected from, with the intention of sequencing, as defined by the country or sea name. country or sea names should be chosen from the insdc country list (http://insdc.org/country.html).</t>
   </si>
   <si>
-    <t>host disease status</t>
+    <t>host_disease_status</t>
   </si>
   <si>
     <t>(Optional) List of diseases with which the host has been diagnosed; can include multiple diagnoses. the value of the field depends on host; for humans the terms should be chosen from do (disease ontology) at http://www.disease-ontology.org, other hosts are free text</t>
@@ -1904,31 +1916,31 @@
     <t>recovered with sequelae</t>
   </si>
   <si>
-    <t>host disease outcome</t>
+    <t>host_disease_outcome</t>
   </si>
   <si>
     <t>(Optional) Disease outcome in the host.</t>
   </si>
   <si>
-    <t>host subject id</t>
+    <t>host_subject_id</t>
   </si>
   <si>
     <t>(Optional) A unique identifier by which each subject can be referred to, de-identified, e.g. #131</t>
   </si>
   <si>
-    <t>host age</t>
+    <t>host_age</t>
   </si>
   <si>
     <t>(Optional) Age of host at the time of sampling; relevant scale depends on species and study, e.g. could be seconds for amoebae or centuries for trees (Units: years)</t>
   </si>
   <si>
-    <t>host taxid</t>
+    <t>host_taxid</t>
   </si>
   <si>
     <t>(Optional) Ncbi taxon id of the host, e.g. 9606</t>
   </si>
   <si>
-    <t>host life stage</t>
+    <t>host_life_stage</t>
   </si>
   <si>
     <t>(Optional) Description of life stage of host</t>
@@ -1940,7 +1952,7 @@
     <t>healthy</t>
   </si>
   <si>
-    <t>host health state</t>
+    <t>host_health_state</t>
   </si>
   <si>
     <t>(Mandatory) Health status of the host at the time of sample collection.</t>
@@ -1958,7 +1970,7 @@
     <t>neuter</t>
   </si>
   <si>
-    <t>host sex</t>
+    <t>host_sex</t>
   </si>
   <si>
     <t>(Optional) Gender or sex of the host.</t>
@@ -1970,7 +1982,7 @@
     <t>(Optional) Scientific name of the laboratory host used to propagate the source organism from which the sample was obtained</t>
   </si>
   <si>
-    <t>host scientific name</t>
+    <t>host_scientific_name</t>
   </si>
   <si>
     <t>(Mandatory) Scientific name of the natural (as opposed to laboratory) host to the organism from which sample was obtained.</t>
@@ -1982,7 +1994,7 @@
     <t>(Optional) Details of passage of culture between time of isolation and sequencing</t>
   </si>
   <si>
-    <t>Is the sequenced pathogen host associated?</t>
+    <t>is_the_sequenced_pathogen_host_associated</t>
   </si>
   <si>
     <t>(Mandatory) Is the sequenced pathogen host associated? ('yes' or 'no')</t>
@@ -2048,19 +2060,19 @@
     <t>(Recommended) Name of the strain from which the sample was obtained.</t>
   </si>
   <si>
-    <t>host disease stage</t>
+    <t>host_disease_stage</t>
   </si>
   <si>
     <t>(Optional) Disease stage of host</t>
   </si>
   <si>
-    <t>isolation source host-associated</t>
+    <t>isolation_source_hostassociated</t>
   </si>
   <si>
     <t>(Recommended) Name of host tissue or organ sampled for analysis. example: tracheal tissue</t>
   </si>
   <si>
-    <t>host description</t>
+    <t>host_description</t>
   </si>
   <si>
     <t>(Optional) Other descriptive information relating to the host.</t>
@@ -2072,7 +2084,7 @@
     <t>(Optional) Name or code for genotype of organism</t>
   </si>
   <si>
-    <t>isolation source non-host-associated</t>
+    <t>isolation_source_nonhostassociated</t>
   </si>
   <si>
     <t>(Recommended) Describes the physical, environmental and/or local geographical source of the biological sample from which the sample was derived. example: soil</t>
@@ -2081,7 +2093,7 @@
     <t>depth</t>
   </si>
   <si>
-    <t>(Optional) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: mm)</t>
+    <t>(Optional) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: m)</t>
   </si>
 </sst>
 </file>
@@ -2611,7 +2623,7 @@
         <v>143</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2655,7 +2667,7 @@
         <v>144</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -2682,7 +2694,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N86"/>
+  <dimension ref="G1:N87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3406,6 +3418,11 @@
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="87" spans="14:14">
+      <c r="N87" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3427,27 +3444,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3467,122 +3484,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -3606,300 +3623,300 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
     </row>
     <row r="2" spans="1:50" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="AJ2" s="2" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="AK2" s="2" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="AL2" s="2" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="AM2" s="2" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="AN2" s="2" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="AO2" s="2" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="AP2" s="2" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="AQ2" s="2" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="AR2" s="2" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="AS2" s="2" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="AT2" s="2" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="AU2" s="2" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="AV2" s="2" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="AW2" s="2" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="AX2" s="2" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
     </row>
   </sheetData>
@@ -3929,7 +3946,7 @@
       <formula1>hostsex</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH3:AH101">
-      <formula1>Isthesequencedpathogenhostassociated</formula1>
+      <formula1>isthesequencedpathogenhostassociated</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3938,258 +3955,258 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:AH289"/>
+  <dimension ref="G1:AH294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:34">
       <c r="G1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="I1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="S1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="V1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X1" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="AC1" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="AD1" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="AH1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="2" spans="7:34">
       <c r="G2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="S2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="V2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="X2" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="AC2" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="AD2" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="AH2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="3" spans="7:34">
       <c r="G3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="V3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="X3" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="AC3" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="AD3" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
     </row>
     <row r="4" spans="7:34">
       <c r="I4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="V4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AC4" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="AD4" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
     </row>
     <row r="5" spans="7:34">
       <c r="I5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="V5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AC5" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="AD5" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
     </row>
     <row r="6" spans="7:34">
       <c r="I6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="V6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AC6" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="AD6" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
     </row>
     <row r="7" spans="7:34">
       <c r="I7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="V7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AC7" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="AD7" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
     </row>
     <row r="8" spans="7:34">
       <c r="I8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="V8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AC8" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="AD8" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
     </row>
     <row r="9" spans="7:34">
       <c r="I9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="V9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AC9" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="AD9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
     </row>
     <row r="10" spans="7:34">
       <c r="I10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="V10" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AC10" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="AD10" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
     </row>
     <row r="11" spans="7:34">
       <c r="I11" t="s">
+        <v>293</v>
+      </c>
+      <c r="V11" t="s">
         <v>292</v>
       </c>
-      <c r="V11" t="s">
-        <v>291</v>
-      </c>
       <c r="AC11" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="AD11" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
     </row>
     <row r="12" spans="7:34">
       <c r="I12" t="s">
+        <v>294</v>
+      </c>
+      <c r="V12" t="s">
         <v>293</v>
       </c>
-      <c r="V12" t="s">
-        <v>292</v>
-      </c>
       <c r="AC12" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="AD12" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
     </row>
     <row r="13" spans="7:34">
       <c r="I13" t="s">
+        <v>295</v>
+      </c>
+      <c r="V13" t="s">
         <v>294</v>
       </c>
-      <c r="V13" t="s">
-        <v>293</v>
-      </c>
       <c r="AC13" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="AD13" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
     </row>
     <row r="14" spans="7:34">
       <c r="I14" t="s">
+        <v>296</v>
+      </c>
+      <c r="V14" t="s">
         <v>295</v>
       </c>
-      <c r="V14" t="s">
-        <v>294</v>
-      </c>
       <c r="AC14" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="AD14" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
     </row>
     <row r="15" spans="7:34">
       <c r="I15" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="V15" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AD15" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
     </row>
     <row r="16" spans="7:34">
       <c r="I16" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="V16" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AD16" t="s">
         <v>116</v>
@@ -4197,1050 +4214,1050 @@
     </row>
     <row r="17" spans="9:30">
       <c r="I17" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="V17" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AD17" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
     </row>
     <row r="18" spans="9:30">
       <c r="I18" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="V18" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="19" spans="9:30">
       <c r="I19" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="V19" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="20" spans="9:30">
       <c r="I20" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="V20" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="21" spans="9:30">
       <c r="I21" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="V21" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="22" spans="9:30">
       <c r="I22" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="V22" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="23" spans="9:30">
       <c r="I23" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="V23" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="24" spans="9:30">
       <c r="I24" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="V24" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="25" spans="9:30">
       <c r="I25" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="V25" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="26" spans="9:30">
       <c r="I26" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="V26" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="27" spans="9:30">
       <c r="I27" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="V27" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="28" spans="9:30">
       <c r="I28" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="V28" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="29" spans="9:30">
       <c r="I29" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="V29" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="30" spans="9:30">
       <c r="I30" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="V30" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="31" spans="9:30">
       <c r="I31" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="V31" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="32" spans="9:30">
       <c r="I32" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="V32" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="33" spans="9:22">
       <c r="I33" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="V33" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="34" spans="9:22">
       <c r="I34" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="V34" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="35" spans="9:22">
       <c r="I35" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="V35" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="36" spans="9:22">
       <c r="I36" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="V36" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="37" spans="9:22">
       <c r="I37" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="V37" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="38" spans="9:22">
       <c r="I38" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="V38" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="39" spans="9:22">
       <c r="I39" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="V39" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="40" spans="9:22">
       <c r="I40" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="V40" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="41" spans="9:22">
       <c r="I41" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="V41" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="42" spans="9:22">
       <c r="I42" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="V42" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="43" spans="9:22">
       <c r="I43" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="V43" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="44" spans="9:22">
       <c r="I44" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="V44" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="45" spans="9:22">
       <c r="I45" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="V45" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="46" spans="9:22">
       <c r="I46" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="V46" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="47" spans="9:22">
       <c r="I47" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="V47" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="48" spans="9:22">
       <c r="I48" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="V48" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="49" spans="9:22">
       <c r="I49" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="V49" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="50" spans="9:22">
       <c r="I50" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="V50" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="51" spans="9:22">
       <c r="I51" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="V51" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="52" spans="9:22">
       <c r="I52" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="V52" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="53" spans="9:22">
       <c r="I53" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="V53" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="54" spans="9:22">
       <c r="I54" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="V54" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="55" spans="9:22">
       <c r="I55" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="V55" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="56" spans="9:22">
       <c r="I56" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="V56" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="57" spans="9:22">
       <c r="I57" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="V57" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="58" spans="9:22">
       <c r="I58" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="V58" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="59" spans="9:22">
       <c r="I59" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="V59" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="60" spans="9:22">
       <c r="I60" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="V60" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="61" spans="9:22">
       <c r="I61" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="V61" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="62" spans="9:22">
       <c r="I62" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="V62" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="63" spans="9:22">
       <c r="I63" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="V63" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="64" spans="9:22">
       <c r="I64" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="V64" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="65" spans="9:22">
       <c r="I65" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="V65" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="66" spans="9:22">
       <c r="I66" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="V66" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="67" spans="9:22">
       <c r="I67" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="V67" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="68" spans="9:22">
       <c r="I68" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="V68" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="69" spans="9:22">
       <c r="I69" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="V69" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="70" spans="9:22">
       <c r="I70" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="V70" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="71" spans="9:22">
       <c r="I71" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="V71" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="72" spans="9:22">
       <c r="I72" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="V72" t="s">
-        <v>589</v>
+        <v>350</v>
       </c>
     </row>
     <row r="73" spans="9:22">
       <c r="I73" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="V73" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="74" spans="9:22">
       <c r="I74" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="V74" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="75" spans="9:22">
       <c r="I75" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="V75" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="76" spans="9:22">
       <c r="I76" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="V76" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="77" spans="9:22">
       <c r="I77" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="V77" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="78" spans="9:22">
       <c r="I78" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="V78" t="s">
-        <v>354</v>
+        <v>590</v>
       </c>
     </row>
     <row r="79" spans="9:22">
       <c r="I79" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="V79" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="80" spans="9:22">
       <c r="I80" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="V80" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="81" spans="9:22">
       <c r="I81" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="V81" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="82" spans="9:22">
       <c r="I82" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="V82" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="83" spans="9:22">
       <c r="I83" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="V83" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="84" spans="9:22">
       <c r="I84" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="V84" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="85" spans="9:22">
       <c r="I85" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="V85" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="86" spans="9:22">
       <c r="I86" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="V86" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="87" spans="9:22">
       <c r="I87" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="V87" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="88" spans="9:22">
       <c r="I88" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="V88" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="89" spans="9:22">
       <c r="I89" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="V89" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="90" spans="9:22">
       <c r="I90" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="V90" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="91" spans="9:22">
       <c r="I91" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="V91" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="92" spans="9:22">
       <c r="I92" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="V92" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="93" spans="9:22">
       <c r="I93" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="V93" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="94" spans="9:22">
       <c r="I94" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="V94" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="95" spans="9:22">
       <c r="I95" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="V95" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="96" spans="9:22">
       <c r="I96" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="V96" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="97" spans="9:22">
       <c r="I97" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="V97" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="98" spans="9:22">
       <c r="I98" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="V98" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="99" spans="9:22">
       <c r="I99" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="V99" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="100" spans="9:22">
       <c r="I100" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="V100" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="101" spans="9:22">
       <c r="I101" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="V101" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="102" spans="9:22">
       <c r="I102" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="V102" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="103" spans="9:22">
       <c r="I103" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="V103" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="104" spans="9:22">
       <c r="I104" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="V104" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="105" spans="9:22">
       <c r="I105" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="V105" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="106" spans="9:22">
       <c r="I106" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="V106" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="107" spans="9:22">
       <c r="I107" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="V107" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="108" spans="9:22">
       <c r="I108" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="V108" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="109" spans="9:22">
       <c r="I109" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="V109" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="110" spans="9:22">
       <c r="I110" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="V110" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="111" spans="9:22">
       <c r="I111" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="V111" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="112" spans="9:22">
       <c r="I112" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="V112" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="113" spans="9:22">
       <c r="I113" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="V113" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="114" spans="9:22">
       <c r="I114" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="V114" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="115" spans="9:22">
       <c r="I115" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="V115" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="116" spans="9:22">
       <c r="I116" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="V116" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="117" spans="9:22">
       <c r="I117" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="V117" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="118" spans="9:22">
       <c r="I118" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="V118" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="119" spans="9:22">
       <c r="I119" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="V119" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="120" spans="9:22">
       <c r="I120" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="V120" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="121" spans="9:22">
       <c r="I121" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="V121" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="122" spans="9:22">
       <c r="I122" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="V122" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="123" spans="9:22">
       <c r="I123" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="V123" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="124" spans="9:22">
       <c r="I124" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="V124" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="125" spans="9:22">
       <c r="I125" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="V125" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="126" spans="9:22">
       <c r="I126" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="V126" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="127" spans="9:22">
       <c r="I127" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="V127" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="128" spans="9:22">
       <c r="I128" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="V128" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="129" spans="9:22">
       <c r="I129" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="V129" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="130" spans="9:22">
       <c r="I130" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="V130" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="131" spans="9:22">
       <c r="I131" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="V131" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="132" spans="9:22">
       <c r="I132" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="V132" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="133" spans="9:22">
       <c r="I133" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="V133" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="134" spans="9:22">
       <c r="I134" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="V134" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="135" spans="9:22">
       <c r="I135" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="V135" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="136" spans="9:22">
       <c r="I136" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="V136" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="137" spans="9:22">
       <c r="I137" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="V137" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="138" spans="9:22">
       <c r="I138" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="V138" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="139" spans="9:22">
       <c r="I139" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="V139" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="140" spans="9:22">
       <c r="I140" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="V140" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="141" spans="9:22">
       <c r="I141" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="V141" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="142" spans="9:22">
       <c r="I142" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="V142" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="143" spans="9:22">
       <c r="I143" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="V143" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="144" spans="9:22">
       <c r="I144" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="V144" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="145" spans="9:22">
       <c r="I145" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="V145" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="146" spans="9:22">
       <c r="I146" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="V146" t="s">
-        <v>424</v>
+        <v>594</v>
       </c>
     </row>
     <row r="147" spans="9:22">
       <c r="I147" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="V147" t="s">
         <v>425</v>
@@ -5248,7 +5265,7 @@
     </row>
     <row r="148" spans="9:22">
       <c r="I148" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="V148" t="s">
         <v>426</v>
@@ -5256,7 +5273,7 @@
     </row>
     <row r="149" spans="9:22">
       <c r="I149" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="V149" t="s">
         <v>427</v>
@@ -5264,311 +5281,311 @@
     </row>
     <row r="150" spans="9:22">
       <c r="I150" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="V150" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="151" spans="9:22">
       <c r="I151" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="V151" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="152" spans="9:22">
       <c r="I152" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="V152" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="153" spans="9:22">
       <c r="I153" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="V153" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="154" spans="9:22">
       <c r="I154" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="V154" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="155" spans="9:22">
       <c r="I155" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="V155" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="156" spans="9:22">
       <c r="I156" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="V156" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="157" spans="9:22">
       <c r="I157" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="V157" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="158" spans="9:22">
       <c r="I158" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="V158" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="159" spans="9:22">
       <c r="I159" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="V159" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="160" spans="9:22">
       <c r="I160" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="V160" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="161" spans="9:22">
       <c r="I161" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="V161" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="162" spans="9:22">
       <c r="I162" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="V162" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="163" spans="9:22">
       <c r="I163" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="V163" t="s">
-        <v>440</v>
+        <v>596</v>
       </c>
     </row>
     <row r="164" spans="9:22">
       <c r="I164" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="V164" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="165" spans="9:22">
       <c r="I165" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="V165" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="166" spans="9:22">
       <c r="I166" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="V166" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="167" spans="9:22">
       <c r="I167" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="V167" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="168" spans="9:22">
       <c r="I168" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="V168" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="169" spans="9:22">
       <c r="I169" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="V169" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="170" spans="9:22">
       <c r="I170" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="V170" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="171" spans="9:22">
       <c r="I171" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="V171" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="172" spans="9:22">
       <c r="I172" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="V172" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
     </row>
     <row r="173" spans="9:22">
       <c r="I173" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="V173" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="174" spans="9:22">
       <c r="I174" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="V174" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="175" spans="9:22">
       <c r="I175" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="V175" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="176" spans="9:22">
       <c r="I176" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="V176" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="177" spans="9:22">
       <c r="I177" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="V177" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="178" spans="9:22">
       <c r="I178" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="V178" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="179" spans="9:22">
       <c r="I179" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="V179" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="180" spans="9:22">
       <c r="I180" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="V180" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="181" spans="9:22">
       <c r="I181" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="V181" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="182" spans="9:22">
       <c r="I182" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="V182" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="183" spans="9:22">
       <c r="I183" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="V183" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="184" spans="9:22">
       <c r="I184" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="V184" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="185" spans="9:22">
       <c r="I185" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="V185" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="186" spans="9:22">
       <c r="I186" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="V186" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
     </row>
     <row r="187" spans="9:22">
       <c r="I187" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="V187" t="s">
-        <v>463</v>
+        <v>599</v>
       </c>
     </row>
     <row r="188" spans="9:22">
       <c r="I188" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="V188" t="s">
         <v>464</v>
@@ -5576,7 +5593,7 @@
     </row>
     <row r="189" spans="9:22">
       <c r="I189" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="V189" t="s">
         <v>465</v>
@@ -5584,23 +5601,23 @@
     </row>
     <row r="190" spans="9:22">
       <c r="I190" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="V190" t="s">
-        <v>596</v>
+        <v>466</v>
       </c>
     </row>
     <row r="191" spans="9:22">
       <c r="I191" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="V191" t="s">
-        <v>466</v>
+        <v>600</v>
       </c>
     </row>
     <row r="192" spans="9:22">
       <c r="I192" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="V192" t="s">
         <v>467</v>
@@ -5608,7 +5625,7 @@
     </row>
     <row r="193" spans="9:22">
       <c r="I193" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="V193" t="s">
         <v>468</v>
@@ -5616,7 +5633,7 @@
     </row>
     <row r="194" spans="9:22">
       <c r="I194" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="V194" t="s">
         <v>469</v>
@@ -5624,7 +5641,7 @@
     </row>
     <row r="195" spans="9:22">
       <c r="I195" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="V195" t="s">
         <v>470</v>
@@ -5632,7 +5649,7 @@
     </row>
     <row r="196" spans="9:22">
       <c r="I196" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="V196" t="s">
         <v>471</v>
@@ -5640,7 +5657,7 @@
     </row>
     <row r="197" spans="9:22">
       <c r="I197" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="V197" t="s">
         <v>472</v>
@@ -5648,7 +5665,7 @@
     </row>
     <row r="198" spans="9:22">
       <c r="I198" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="V198" t="s">
         <v>473</v>
@@ -5656,7 +5673,7 @@
     </row>
     <row r="199" spans="9:22">
       <c r="I199" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="V199" t="s">
         <v>474</v>
@@ -5664,7 +5681,7 @@
     </row>
     <row r="200" spans="9:22">
       <c r="I200" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="V200" t="s">
         <v>475</v>
@@ -5672,7 +5689,7 @@
     </row>
     <row r="201" spans="9:22">
       <c r="I201" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="V201" t="s">
         <v>476</v>
@@ -5680,7 +5697,7 @@
     </row>
     <row r="202" spans="9:22">
       <c r="I202" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="V202" t="s">
         <v>477</v>
@@ -5688,7 +5705,7 @@
     </row>
     <row r="203" spans="9:22">
       <c r="I203" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="V203" t="s">
         <v>478</v>
@@ -5696,7 +5713,7 @@
     </row>
     <row r="204" spans="9:22">
       <c r="I204" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="V204" t="s">
         <v>479</v>
@@ -5704,7 +5721,7 @@
     </row>
     <row r="205" spans="9:22">
       <c r="I205" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="V205" t="s">
         <v>480</v>
@@ -5712,7 +5729,7 @@
     </row>
     <row r="206" spans="9:22">
       <c r="I206" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="V206" t="s">
         <v>481</v>
@@ -5720,7 +5737,7 @@
     </row>
     <row r="207" spans="9:22">
       <c r="I207" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="V207" t="s">
         <v>482</v>
@@ -5728,23 +5745,23 @@
     </row>
     <row r="208" spans="9:22">
       <c r="I208" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="V208" t="s">
-        <v>597</v>
+        <v>483</v>
       </c>
     </row>
     <row r="209" spans="9:22">
       <c r="I209" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="V209" t="s">
-        <v>483</v>
+        <v>601</v>
       </c>
     </row>
     <row r="210" spans="9:22">
       <c r="I210" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="V210" t="s">
         <v>484</v>
@@ -5752,586 +5769,611 @@
     </row>
     <row r="211" spans="9:22">
       <c r="I211" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="V211" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="212" spans="9:22">
       <c r="I212" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="V212" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="213" spans="9:22">
       <c r="I213" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="V213" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="214" spans="9:22">
       <c r="I214" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="V214" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="215" spans="9:22">
       <c r="I215" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="V215" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="216" spans="9:22">
       <c r="I216" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="V216" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="217" spans="9:22">
       <c r="I217" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="V217" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="218" spans="9:22">
       <c r="I218" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="V218" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="219" spans="9:22">
       <c r="I219" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="V219" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="220" spans="9:22">
       <c r="I220" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="V220" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
     </row>
     <row r="221" spans="9:22">
       <c r="I221" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="V221" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="222" spans="9:22">
       <c r="I222" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="V222" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="223" spans="9:22">
       <c r="I223" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="V223" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="224" spans="9:22">
       <c r="I224" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="V224" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="225" spans="9:22">
       <c r="I225" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="V225" t="s">
-        <v>598</v>
+        <v>500</v>
       </c>
     </row>
     <row r="226" spans="9:22">
       <c r="I226" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="V226" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="227" spans="9:22">
       <c r="I227" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="V227" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="228" spans="9:22">
       <c r="I228" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="V228" t="s">
-        <v>504</v>
+        <v>602</v>
       </c>
     </row>
     <row r="229" spans="9:22">
       <c r="I229" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="V229" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="230" spans="9:22">
       <c r="I230" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="V230" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="231" spans="9:22">
       <c r="I231" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="V231" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="232" spans="9:22">
       <c r="I232" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="V232" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="233" spans="9:22">
       <c r="I233" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="V233" t="s">
-        <v>599</v>
+        <v>507</v>
       </c>
     </row>
     <row r="234" spans="9:22">
       <c r="I234" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="V234" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="235" spans="9:22">
       <c r="I235" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="V235" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="236" spans="9:22">
       <c r="I236" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="V236" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="237" spans="9:22">
       <c r="I237" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="V237" t="s">
-        <v>514</v>
+        <v>603</v>
       </c>
     </row>
     <row r="238" spans="9:22">
       <c r="I238" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="V238" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
     </row>
     <row r="239" spans="9:22">
       <c r="I239" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="V239" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
     </row>
     <row r="240" spans="9:22">
       <c r="I240" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="V240" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
     </row>
     <row r="241" spans="9:22">
       <c r="I241" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="V241" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
     </row>
     <row r="242" spans="9:22">
       <c r="I242" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="V242" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
     </row>
     <row r="243" spans="9:22">
       <c r="I243" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="V243" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
     </row>
     <row r="244" spans="9:22">
       <c r="I244" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="V244" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
     </row>
     <row r="245" spans="9:22">
       <c r="I245" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="V245" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="246" spans="9:22">
       <c r="I246" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="V246" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="247" spans="9:22">
       <c r="I247" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="V247" t="s">
-        <v>600</v>
+        <v>521</v>
       </c>
     </row>
     <row r="248" spans="9:22">
       <c r="I248" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="V248" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="249" spans="9:22">
       <c r="I249" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="V249" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="250" spans="9:22">
       <c r="I250" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="V250" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
     </row>
     <row r="251" spans="9:22">
       <c r="I251" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="V251" t="s">
-        <v>528</v>
+        <v>604</v>
       </c>
     </row>
     <row r="252" spans="9:22">
       <c r="I252" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="V252" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
     </row>
     <row r="253" spans="9:22">
       <c r="I253" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="V253" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
     </row>
     <row r="254" spans="9:22">
       <c r="I254" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="V254" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
     </row>
     <row r="255" spans="9:22">
       <c r="I255" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="V255" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
     </row>
     <row r="256" spans="9:22">
       <c r="I256" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="V256" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
     </row>
     <row r="257" spans="9:22">
       <c r="I257" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="V257" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
     </row>
     <row r="258" spans="9:22">
       <c r="I258" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="V258" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
     </row>
     <row r="259" spans="9:22">
       <c r="I259" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="V259" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
     </row>
     <row r="260" spans="9:22">
       <c r="I260" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="V260" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
     </row>
     <row r="261" spans="9:22">
       <c r="I261" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="V261" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
     </row>
     <row r="262" spans="9:22">
       <c r="I262" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="V262" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
     </row>
     <row r="263" spans="9:22">
       <c r="I263" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="V263" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
     </row>
     <row r="264" spans="9:22">
       <c r="I264" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="V264" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
     </row>
     <row r="265" spans="9:22">
       <c r="I265" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="V265" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
     </row>
     <row r="266" spans="9:22">
       <c r="I266" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="V266" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
     </row>
     <row r="267" spans="9:22">
       <c r="I267" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="V267" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
     </row>
     <row r="268" spans="9:22">
       <c r="I268" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="V268" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
     </row>
     <row r="269" spans="9:22">
       <c r="I269" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="V269" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
     </row>
     <row r="270" spans="9:22">
       <c r="I270" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="V270" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
     </row>
     <row r="271" spans="9:22">
       <c r="I271" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="V271" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
     </row>
     <row r="272" spans="9:22">
       <c r="I272" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="V272" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
     </row>
     <row r="273" spans="9:22">
       <c r="I273" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="V273" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
     </row>
     <row r="274" spans="9:22">
       <c r="V274" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="275" spans="9:22">
       <c r="V275" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
     </row>
     <row r="276" spans="9:22">
       <c r="V276" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
     </row>
     <row r="277" spans="9:22">
       <c r="V277" t="s">
-        <v>601</v>
+        <v>551</v>
       </c>
     </row>
     <row r="278" spans="9:22">
       <c r="V278" t="s">
-        <v>602</v>
+        <v>552</v>
       </c>
     </row>
     <row r="279" spans="9:22">
       <c r="V279" t="s">
-        <v>603</v>
+        <v>553</v>
       </c>
     </row>
     <row r="280" spans="9:22">
       <c r="V280" t="s">
-        <v>604</v>
+        <v>554</v>
       </c>
     </row>
     <row r="281" spans="9:22">
       <c r="V281" t="s">
-        <v>605</v>
+        <v>555</v>
       </c>
     </row>
     <row r="282" spans="9:22">
       <c r="V282" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="283" spans="9:22">
       <c r="V283" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="284" spans="9:22">
       <c r="V284" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="285" spans="9:22">
       <c r="V285" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="286" spans="9:22">
       <c r="V286" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="287" spans="9:22">
       <c r="V287" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="288" spans="9:22">
       <c r="V288" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="289" spans="22:22">
       <c r="V289" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="290" spans="22:22">
+      <c r="V290" t="s">
         <v>613</v>
+      </c>
+    </row>
+    <row r="291" spans="22:22">
+      <c r="V291" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="292" spans="22:22">
+      <c r="V292" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="293" spans="22:22">
+      <c r="V293" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="294" spans="22:22">
+      <c r="V294" t="s">
+        <v>617</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000029/metadata_template_ERC000029.xlsx
+++ b/templates/ERC000029/metadata_template_ERC000029.xlsx
@@ -1778,13 +1778,13 @@
     <t>subject exposure duration</t>
   </si>
   <si>
-    <t>(Optional) Duration of the exposure of the subject to an infected human or animal. if multiple exposures are applicable, please state their duration in the same order in which you reported the exposure in the field 'subject exposure'. example: 1 day; 0.33 days (Units: year)</t>
+    <t>(Optional) Duration of the exposure of the subject to an infected human or animal. if multiple exposures are applicable, please state their duration in the same order in which you reported the exposure in the field 'subject exposure'. example: 1 day; 0.33 days (Units: day)</t>
   </si>
   <si>
     <t>amount or size of sample collected</t>
   </si>
   <si>
-    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: m3)</t>
+    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: kg)</t>
   </si>
   <si>
     <t>No</t>
@@ -2111,7 +2111,7 @@
     <t>depth</t>
   </si>
   <si>
-    <t>(Optional) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: mm)</t>
+    <t>(Optional) The vertical distance below local surface, e.g. for sediment or soil samples depth is measured from sediment or soil surface, respectively. depth can be reported as an interval for subsurface samples. (Units: m)</t>
   </si>
 </sst>
 </file>
